--- a/data/trans_orig/IQ22A-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IQ22A-Estudios-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según del número de veces que utilizaron dicho servicio de urgencias</t>
+          <t>Menores según del número de veces que utilizaron dicho servicio de urgencias (tasa de respuesta: 93,84%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,72</t>
+          <t>1,0; 1,64</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,8; 4,23</t>
+          <t>1,8; 4,03</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,24; 3,79</t>
+          <t>1,17; 3,82</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,23; 3,8</t>
+          <t>1,24; 3,92</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,05; 1,55</t>
+          <t>1,05; 1,58</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,44; 2,93</t>
+          <t>1,45; 2,83</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,0; 4,37</t>
+          <t>1,0; 4,29</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,25; 2,5</t>
+          <t>1,3; 2,75</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,08; 1,47</t>
+          <t>1,07; 1,44</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,78; 3,06</t>
+          <t>1,76; 3,05</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,37; 3,42</t>
+          <t>1,45; 3,41</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,46; 2,44</t>
+          <t>1,44; 2,48</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,46; 2,0</t>
+          <t>1,48; 2,04</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,61; 2,2</t>
+          <t>1,62; 2,21</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,74; 2,65</t>
+          <t>1,69; 2,61</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,46; 2,26</t>
+          <t>1,45; 2,24</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,53; 1,9</t>
+          <t>1,51; 1,88</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,51; 1,91</t>
+          <t>1,51; 1,92</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,52; 2,03</t>
+          <t>1,54; 2,05</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,41; 2,01</t>
+          <t>1,4; 1,95</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,54; 1,87</t>
+          <t>1,55; 1,87</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,58; 1,92</t>
+          <t>1,59; 1,95</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,67; 2,16</t>
+          <t>1,68; 2,19</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,51; 1,97</t>
+          <t>1,5; 1,96</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,21; 1,69</t>
+          <t>1,23; 1,7</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,54; 2,67</t>
+          <t>1,55; 2,64</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,45; 2,08</t>
+          <t>1,43; 2,08</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,43; 2,86</t>
+          <t>1,43; 2,89</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,47; 2,11</t>
+          <t>1,47; 2,08</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,29; 1,89</t>
+          <t>1,29; 1,86</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,61; 2,97</t>
+          <t>1,59; 2,78</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,81; 3,53</t>
+          <t>1,78; 3,32</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,41; 1,82</t>
+          <t>1,4; 1,82</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,49; 2,1</t>
+          <t>1,48; 2,1</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,6; 2,23</t>
+          <t>1,6; 2,26</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,74; 2,8</t>
+          <t>1,75; 2,79</t>
         </is>
       </c>
     </row>
@@ -1136,22 +1136,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,4; 1,79</t>
+          <t>1,41; 1,78</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,72; 2,28</t>
+          <t>1,73; 2,29</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,71; 2,32</t>
+          <t>1,69; 2,34</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,58; 2,19</t>
+          <t>1,56; 2,2</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,53; 1,85</t>
+          <t>1,52; 1,86</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,63; 2,11</t>
+          <t>1,62; 2,13</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1181,17 +1181,17 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,67; 1,95</t>
+          <t>1,67; 1,97</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,72; 2,13</t>
+          <t>1,72; 2,12</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,66; 2,09</t>
+          <t>1,66; 2,07</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ22A-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IQ22A-Estudios-trans_orig.xlsx
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,64</t>
+          <t>1,0; 1,6</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,8; 4,03</t>
+          <t>1,77; 4,22</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,17; 3,82</t>
+          <t>1,19; 3,78</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,24; 3,92</t>
+          <t>1,24; 3,87</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,05; 1,58</t>
+          <t>1,05; 1,57</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,45; 2,83</t>
+          <t>1,43; 2,8</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,0; 4,29</t>
+          <t>1,0; 4,39</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,3; 2,75</t>
+          <t>1,3; 2,51</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,07; 1,44</t>
+          <t>1,08; 1,44</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,76; 3,05</t>
+          <t>1,71; 3,11</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,45; 3,41</t>
+          <t>1,42; 3,44</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,44; 2,48</t>
+          <t>1,45; 2,56</t>
         </is>
       </c>
     </row>
@@ -856,27 +856,27 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,48; 2,04</t>
+          <t>1,49; 2,02</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,62; 2,21</t>
+          <t>1,6; 2,18</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,69; 2,61</t>
+          <t>1,71; 2,61</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,45; 2,24</t>
+          <t>1,47; 2,27</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,51; 1,88</t>
+          <t>1,52; 1,9</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -886,27 +886,27 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,54; 2,05</t>
+          <t>1,52; 2,04</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,4; 1,95</t>
+          <t>1,41; 2,01</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,55; 1,87</t>
+          <t>1,55; 1,86</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,59; 1,95</t>
+          <t>1,59; 1,9</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,68; 2,19</t>
+          <t>1,68; 2,17</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -996,17 +996,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,23; 1,7</t>
+          <t>1,22; 1,75</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,55; 2,64</t>
+          <t>1,54; 2,63</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,43; 2,08</t>
+          <t>1,43; 2,12</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1016,42 +1016,42 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,47; 2,08</t>
+          <t>1,48; 2,11</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,29; 1,86</t>
+          <t>1,3; 1,9</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,59; 2,78</t>
+          <t>1,61; 2,82</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,78; 3,32</t>
+          <t>1,79; 3,3</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,4; 1,82</t>
+          <t>1,41; 1,82</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,48; 2,1</t>
+          <t>1,49; 2,1</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,6; 2,26</t>
+          <t>1,6; 2,33</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,75; 2,79</t>
+          <t>1,76; 2,74</t>
         </is>
       </c>
     </row>
@@ -1136,37 +1136,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,41; 1,78</t>
+          <t>1,42; 1,8</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,73; 2,29</t>
+          <t>1,73; 2,27</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,69; 2,34</t>
+          <t>1,68; 2,33</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,56; 2,2</t>
+          <t>1,61; 2,2</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,52; 1,82</t>
+          <t>1,51; 1,81</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,52; 1,86</t>
+          <t>1,53; 1,87</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,62; 2,13</t>
+          <t>1,61; 2,13</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1176,22 +1176,22 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,51; 1,75</t>
+          <t>1,51; 1,74</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,67; 1,97</t>
+          <t>1,67; 1,95</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,72; 2,12</t>
+          <t>1,74; 2,13</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,66; 2,07</t>
+          <t>1,67; 2,09</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ22A-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IQ22A-Estudios-trans_orig.xlsx
@@ -532,7 +532,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -540,7 +540,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -648,54 +648,54 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1,21</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1,92</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2,21</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1,61</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>1,17</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>2,55</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>1,99</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2,0</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>1,21</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1,92</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1,85</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>1,19</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>2,21</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>1,69</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>1,19</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>2,21</t>
-        </is>
-      </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
           <t>2,08</t>
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,84</t>
+          <t>1,7</t>
         </is>
       </c>
     </row>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,6</t>
+          <t>1,05; 1,55</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,77; 4,22</t>
+          <t>1,44; 2,93</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,19; 3,78</t>
+          <t>1,0; 4,37</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,24; 3,87</t>
+          <t>1,19; 2,4</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,05; 1,57</t>
+          <t>1,0; 1,72</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,43; 2,8</t>
+          <t>1,8; 4,23</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,0; 4,39</t>
+          <t>1,24; 3,79</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,3; 2,51</t>
+          <t>1,16; 3,65</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,08; 1,44</t>
+          <t>1,08; 1,47</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,71; 3,11</t>
+          <t>1,78; 3,06</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,42; 3,44</t>
+          <t>1,37; 3,42</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,45; 2,56</t>
+          <t>1,29; 2,43</t>
         </is>
       </c>
     </row>
@@ -793,57 +793,57 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>1,67</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1,73</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>1,62</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>1,68</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
           <t>1,83</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>2,01</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>1,76</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>1,74</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>1,68</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>1,67</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>1,73</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>1,65</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>1,74</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>1,87</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>1,68</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>1,74</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>1,87</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>1,7</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,49; 2,02</t>
+          <t>1,53; 1,9</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,6; 2,18</t>
+          <t>1,51; 1,91</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,71; 2,61</t>
+          <t>1,52; 2,03</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,47; 2,27</t>
+          <t>1,39; 1,94</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,52; 1,9</t>
+          <t>1,46; 2,0</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,51; 1,92</t>
+          <t>1,61; 2,2</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,52; 2,04</t>
+          <t>1,74; 2,65</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,41; 2,01</t>
+          <t>1,46; 2,3</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,55; 1,86</t>
+          <t>1,54; 1,87</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,59; 1,9</t>
+          <t>1,58; 1,92</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,68; 2,17</t>
+          <t>1,67; 2,16</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,5; 1,96</t>
+          <t>1,49; 1,96</t>
         </is>
       </c>
     </row>
@@ -928,42 +928,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>1,73</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1,49</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2,0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>2,42</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>1,4</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>1,93</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>1,69</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1,91</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>1,73</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>1,49</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>2,0</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2,43</t>
+          <t>1,88</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2,18</t>
+          <t>2,14</t>
         </is>
       </c>
     </row>
@@ -996,44 +996,44 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,22; 1,75</t>
+          <t>1,47; 2,11</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,54; 2,63</t>
+          <t>1,29; 1,89</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,43; 2,12</t>
+          <t>1,61; 2,97</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
+          <t>1,81; 3,52</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>1,21; 1,69</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>1,54; 2,67</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>1,45; 2,08</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>1,43; 2,89</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>1,48; 2,11</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>1,3; 1,9</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>1,61; 2,82</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>1,79; 3,3</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
           <t>1,41; 1,82</t>
@@ -1046,12 +1046,12 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,6; 2,33</t>
+          <t>1,6; 2,23</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,76; 2,74</t>
+          <t>1,73; 2,75</t>
         </is>
       </c>
     </row>
@@ -1068,62 +1068,62 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1,65</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1,67</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1,83</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1,84</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>1,56</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>1,95</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>1,92</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>1,79</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>1,61</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>1,79</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>1,88</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>1,82</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>1,65</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,67</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>1,83</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>1,87</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>1,61</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>1,79</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>1,88</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>1,85</t>
         </is>
       </c>
     </row>
@@ -1136,47 +1136,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,42; 1,8</t>
+          <t>1,52; 1,82</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,73; 2,27</t>
+          <t>1,53; 1,85</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,68; 2,33</t>
+          <t>1,63; 2,11</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,61; 2,2</t>
+          <t>1,59; 2,17</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,51; 1,81</t>
+          <t>1,4; 1,79</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,53; 1,87</t>
+          <t>1,72; 2,28</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,61; 2,13</t>
+          <t>1,71; 2,32</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,63; 2,21</t>
+          <t>1,54; 2,18</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,51; 1,74</t>
+          <t>1,51; 1,75</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1186,12 +1186,12 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,74; 2,13</t>
+          <t>1,72; 2,13</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,67; 2,09</t>
+          <t>1,63; 2,05</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ22A-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IQ22A-Estudios-trans_orig.xlsx
@@ -16,7 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +127,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +140,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N12"/>
+  <dimension ref="A1:N16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -526,7 +531,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según del número de veces que utilizaron dicho servicio de urgencias (tasa de respuesta: 93,84%)</t>
+          <t>Número medio de veces que los menores utilizaron algún servicio de urgencias en los últimos 12 meses (tasa de respuesta: 93,84%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -646,419 +651,271 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>1,21</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>1,92</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2,21</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1,61</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>1,17</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>2,55</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>1,99</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>1,85</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>1,19</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>2,21</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>2,08</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>1,7</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>1.21232817943073</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>1.919270475781089</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>2.209157076678992</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>1.60906684635744</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>1.167183222249998</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>2.545441072833112</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>1.986130087336317</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>1.852076112462818</v>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>1.190511102894372</v>
+      </c>
+      <c r="L4" s="5" t="n">
+        <v>2.21245158754605</v>
+      </c>
+      <c r="M4" s="5" t="n">
+        <v>2.078828045309981</v>
+      </c>
+      <c r="N4" s="5" t="n">
+        <v>1.699296547510686</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>1,05; 1,55</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>1,44; 2,93</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>1,0; 4,37</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>1,19; 2,4</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>1,0; 1,72</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>1,8; 4,23</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>1,24; 3,79</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>1,16; 3,65</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>1,08; 1,47</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>1,78; 3,06</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>1,37; 3,42</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>1,29; 2,43</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>1.053665575578114</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>1.435433131968096</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>1.186666957675174</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>1.797703283606751</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>1.236011147475307</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>1.157120936872065</v>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>1.079054053387886</v>
+      </c>
+      <c r="L5" s="5" t="n">
+        <v>1.77545076678122</v>
+      </c>
+      <c r="M5" s="5" t="n">
+        <v>1.366227466372962</v>
+      </c>
+      <c r="N5" s="5" t="n">
+        <v>1.294564712017448</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>1.551307927860878</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>2.928489551284048</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>4.371375576823835</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>2.398743985508284</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>1.722316160850097</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>4.233352562325621</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>3.78903779720965</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>3.652679864222879</v>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>1.466939546418626</v>
+      </c>
+      <c r="L6" s="5" t="n">
+        <v>3.064219710187769</v>
+      </c>
+      <c r="M6" s="5" t="n">
+        <v>3.419032172953301</v>
+      </c>
+      <c r="N6" s="5" t="n">
+        <v>2.433827373013639</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Secundarios</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>1,68</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>1,67</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>1,73</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>1,62</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>1,68</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>1,83</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>2,01</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>1,74</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>1,68</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>1,74</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>1,87</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>1,68</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>1,53; 1,9</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>1,51; 1,91</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1,52; 2,03</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>1,39; 1,94</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>1,46; 2,0</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>1,61; 2,2</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>1,74; 2,65</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>1,46; 2,3</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>1,54; 1,87</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>1,58; 1,92</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>1,67; 2,16</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,49; 1,96</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>1.681721418906453</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>1.674606904726081</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>1.734182034942698</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>1.620266064280634</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>1.678058507686359</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>1.833370215622309</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>2.014132720460054</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>1.738098355960557</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>1.680042093696546</v>
+      </c>
+      <c r="L7" s="5" t="n">
+        <v>1.742993152406942</v>
+      </c>
+      <c r="M7" s="5" t="n">
+        <v>1.868610151773348</v>
+      </c>
+      <c r="N7" s="5" t="n">
+        <v>1.676542533897861</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>1,73</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>1,49</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>2,0</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>2,42</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>1,4</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>1,93</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>1,69</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>1,88</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>1,58</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>1,71</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>1,84</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>2,14</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>1.528305109938572</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>1.511946915696008</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>1.523589726035628</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>1.392219718142792</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>1.464600271397219</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>1.605859968948823</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>1.73608598342893</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>1.46019553774428</v>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>1.544998766537003</v>
+      </c>
+      <c r="L8" s="5" t="n">
+        <v>1.582549880226139</v>
+      </c>
+      <c r="M8" s="5" t="n">
+        <v>1.668814811992444</v>
+      </c>
+      <c r="N8" s="5" t="n">
+        <v>1.486498107582867</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>1,47; 2,11</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>1,29; 1,89</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>1,61; 2,97</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>1,81; 3,52</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>1,21; 1,69</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>1,54; 2,67</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>1,45; 2,08</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>1,43; 2,89</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>1,41; 1,82</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>1,49; 2,1</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>1,6; 2,23</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>1,73; 2,75</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>1.900387899514111</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>1.90742716187158</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>2.03305594543259</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>1.940240920980982</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>2.003360556702182</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>2.195860313911474</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>2.653306594077967</v>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>2.295772859245828</v>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>1.8696451746024</v>
+      </c>
+      <c r="L9" s="5" t="n">
+        <v>1.922742864441203</v>
+      </c>
+      <c r="M9" s="5" t="n">
+        <v>2.157233598039314</v>
+      </c>
+      <c r="N9" s="5" t="n">
+        <v>1.960688088717123</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Universitarios</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -1066,137 +923,269 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>1,65</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>1,67</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1,83</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>1,84</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>1,56</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,95</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>1,92</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>1,79</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>1,61</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>1,79</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>1,88</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>1,82</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>1.730145041404341</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>1.488106494081493</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>1.995077947734217</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>2.415101002652122</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>1.398294837062936</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>1.925379698354068</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>1.690653956940501</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>1.884161135016669</v>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>1.578466461619682</v>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>1.706342997594243</v>
+      </c>
+      <c r="M10" s="5" t="n">
+        <v>1.841156691680501</v>
+      </c>
+      <c r="N10" s="5" t="n">
+        <v>2.144651523589169</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>1,52; 1,82</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>1,53; 1,85</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>1,63; 2,11</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>1,59; 2,17</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>1,4; 1,79</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>1,72; 2,28</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>1,71; 2,32</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>1,54; 2,18</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>1,51; 1,75</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>1,67; 1,95</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>1,72; 2,13</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>1,63; 2,05</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>1.468465924916859</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>1.292438490374839</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>1.608257783681197</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>1.805501191388039</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>1.206077385052077</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>1.544607853891631</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>1.452937595341178</v>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>1.430452384839349</v>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>1.405194484168212</v>
+      </c>
+      <c r="L11" s="5" t="n">
+        <v>1.490792230230224</v>
+      </c>
+      <c r="M11" s="5" t="n">
+        <v>1.603284173099549</v>
+      </c>
+      <c r="N11" s="5" t="n">
+        <v>1.727717052594444</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>2.106083004352471</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>1.893175956205061</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>2.970751460282851</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>3.519981519577659</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>1.686923087328847</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>2.6735683797145</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>2.083231444233598</v>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>2.887523031818707</v>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>1.82035345326861</v>
+      </c>
+      <c r="L12" s="5" t="n">
+        <v>2.103714956196729</v>
+      </c>
+      <c r="M12" s="5" t="n">
+        <v>2.230158163611464</v>
+      </c>
+      <c r="N12" s="5" t="n">
+        <v>2.754862659361522</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>1.653874766310953</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>1.667052055658169</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>1.829099808388757</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>1.839057176208506</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>1.559246047567587</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>1.95066693665458</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>1.923842161123752</v>
+      </c>
+      <c r="J13" s="5" t="n">
+        <v>1.790663312396934</v>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>1.610314081910222</v>
+      </c>
+      <c r="L13" s="5" t="n">
+        <v>1.794890953538632</v>
+      </c>
+      <c r="M13" s="5" t="n">
+        <v>1.875920111518822</v>
+      </c>
+      <c r="N13" s="5" t="n">
+        <v>1.815892751960453</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>1.517190796475913</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>1.533957283200616</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>1.625350328521838</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>1.594982691911127</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>1.404572583611406</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>1.715364814633934</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>1.707208800738527</v>
+      </c>
+      <c r="J14" s="5" t="n">
+        <v>1.541333776280006</v>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>1.506165429943796</v>
+      </c>
+      <c r="L14" s="5" t="n">
+        <v>1.670005802589399</v>
+      </c>
+      <c r="M14" s="5" t="n">
+        <v>1.720522120322726</v>
+      </c>
+      <c r="N14" s="5" t="n">
+        <v>1.625549578112234</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>1.822096524924422</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>1.850526452158602</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>2.11485078907165</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>2.170824829565978</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>1.792786820444103</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>2.283285123652623</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>2.322561412158959</v>
+      </c>
+      <c r="J15" s="5" t="n">
+        <v>2.175962439952529</v>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>1.747753874559038</v>
+      </c>
+      <c r="L15" s="5" t="n">
+        <v>1.949470704506522</v>
+      </c>
+      <c r="M15" s="5" t="n">
+        <v>2.127419887331808</v>
+      </c>
+      <c r="N15" s="5" t="n">
+        <v>2.052742234079716</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1204,14 +1193,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
     <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
